--- a/CALCULO_NOTAS_POR_PERIODOS_3ER_AN_O_A.xlsx
+++ b/CALCULO_NOTAS_POR_PERIODOS_3ER_AN_O_A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pro/Desktop/carpeta sin título/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pro/Desktop/NOTAS 2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1358801-09D9-2A4B-9873-D68810279B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD9BE2-762F-8740-B57F-FFD8027F46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1760" windowWidth="34700" windowHeight="19160" activeTab="7" xr2:uid="{BF37B4F6-1786-4C58-92C4-B0786BCD6E45}"/>
+    <workbookView xWindow="1140" yWindow="1760" windowWidth="34700" windowHeight="19160" activeTab="7" xr2:uid="{BF37B4F6-1786-4C58-92C4-B0786BCD6E45}"/>
   </bookViews>
   <sheets>
     <sheet name="ESPANOL" sheetId="19" r:id="rId1"/>
@@ -1618,13 +1618,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1642,6 +1651,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1680,28 +1703,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1711,6 +1712,34 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1742,26 +1771,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1770,29 +1779,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
@@ -1800,6 +1786,20 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1810,67 +1810,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2D7EC844-6F26-42B0-B6EE-C43F91CA557C}"/>
   </cellStyles>
-  <dxfs count="107">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
+  <dxfs count="95">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2687,116 +2627,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="113" t="s">
+      <c r="AO1" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -2893,24 +2833,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="114"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="142"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -9833,20 +9773,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="BB1:BB2"/>
-    <mergeCell ref="BC1:BC2"/>
-    <mergeCell ref="AX1:AX2"/>
-    <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="AW1:AW2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AZ1:AZ2"/>
-    <mergeCell ref="BA1:BA2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="AT1:AT2"/>
-    <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="AV1:AV2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
@@ -9859,74 +9785,88 @@
     <mergeCell ref="AC1:AJ1"/>
     <mergeCell ref="AK1:AK2"/>
     <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AZ1:AZ2"/>
+    <mergeCell ref="BA1:BA2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="AT1:AT2"/>
+    <mergeCell ref="AU1:AU2"/>
+    <mergeCell ref="AV1:AV2"/>
+    <mergeCell ref="BB1:BB2"/>
+    <mergeCell ref="BC1:BC2"/>
+    <mergeCell ref="AX1:AX2"/>
+    <mergeCell ref="AY1:AY2"/>
+    <mergeCell ref="AW1:AW2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:F33 M4:N33 AC4:AD33 E34:AJ37 E38:F38 M38:N38 AC38:AD38 AJ38:AJ42 E39:AI42 E43:AJ47">
-    <cfRule type="cellIs" dxfId="106" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="94" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:AI3">
-    <cfRule type="cellIs" dxfId="105" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="104" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:L38">
-    <cfRule type="cellIs" dxfId="103" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="91" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:AB33">
-    <cfRule type="cellIs" dxfId="102" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="90" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38:AB38">
-    <cfRule type="cellIs" dxfId="101" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="2" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AI33">
-    <cfRule type="cellIs" dxfId="100" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AI38">
-    <cfRule type="cellIs" dxfId="99" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AJ33">
-    <cfRule type="cellIs" dxfId="98" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="13" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AP47">
-    <cfRule type="cellIs" dxfId="97" priority="36" operator="lessThan">
+    <cfRule type="cellIs" dxfId="85" priority="36" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO1">
-    <cfRule type="cellIs" dxfId="96" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="84" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="95" priority="34" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="34" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="94" priority="35" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="35" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="93" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="17" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9965,114 +9905,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -10169,24 +10109,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -16851,6 +16791,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -16861,110 +16817,74 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="92" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="91" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="79" priority="15" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:L39">
-    <cfRule type="cellIs" dxfId="90" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="10" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42:L42">
-    <cfRule type="cellIs" dxfId="89" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O5:AB33 O4:R4 T4:Z4 AB4">
-    <cfRule type="cellIs" dxfId="88" priority="14" operator="lessThan">
+  <conditionalFormatting sqref="O4:AB33">
+    <cfRule type="cellIs" dxfId="76" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38:AB39">
-    <cfRule type="cellIs" dxfId="87" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="75" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O42:AB42">
-    <cfRule type="cellIs" dxfId="86" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AI39">
-    <cfRule type="cellIs" dxfId="85" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42:AI42">
-    <cfRule type="cellIs" dxfId="84" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="72" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE5:AJ33 AE4:AF4 AH4 AJ4">
-    <cfRule type="cellIs" dxfId="83" priority="13" operator="lessThan">
+  <conditionalFormatting sqref="AE4:AJ33">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AP47 E4:F33 M4:N33 AC4:AD33 E34:AJ37 E38:F39 M38:N39 AC38:AD39 AJ38:AJ42 E40:AI41 E42:F42 M42:N42 AC42:AD42 E43:AJ47">
-    <cfRule type="cellIs" dxfId="82" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="18" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="81" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="69" priority="16" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="80" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="17" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="79" priority="11" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S4">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA4">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG4">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI4">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="67" priority="11" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16998,114 +16918,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -17202,24 +17122,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -23884,6 +23804,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -23894,115 +23830,59 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="78" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="66" priority="13" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:L33 G4:H4 J4 L4">
-    <cfRule type="cellIs" dxfId="77" priority="16" operator="lessThan">
+  <conditionalFormatting sqref="G4:L33">
+    <cfRule type="cellIs" dxfId="65" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:L39">
-    <cfRule type="cellIs" dxfId="76" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="64" priority="11" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O5:AB33 O4:P4 R4 T4:X4 Z4 AB4">
-    <cfRule type="cellIs" dxfId="75" priority="15" operator="lessThan">
+  <conditionalFormatting sqref="O4:AB33">
+    <cfRule type="cellIs" dxfId="63" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38:AB39">
-    <cfRule type="cellIs" dxfId="74" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="10" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AI39">
-    <cfRule type="cellIs" dxfId="73" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE5:AJ33 AE4:AF4 AH4 AJ4">
-    <cfRule type="cellIs" dxfId="72" priority="14" operator="lessThan">
+  <conditionalFormatting sqref="AE4:AJ33">
+    <cfRule type="cellIs" dxfId="60" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AP47 E4:F33 M4:N33 AC4:AD33 E34:AJ37 E38:F39 M38:N39 AC38:AD39 AJ38:AJ41 E40:AI42 E42:AJ47">
-    <cfRule type="cellIs" dxfId="71" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="19" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="70" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="58" priority="17" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="69" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="57" priority="18" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="68" priority="12" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S4">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y4">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA4">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG4">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI4">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="12" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24036,114 +23916,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -24240,24 +24120,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -30888,6 +30768,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -30898,65 +30794,49 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:F33 E34:AJ47 M4:N33 AC4:AD33">
-    <cfRule type="cellIs" dxfId="67" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="E4:F33 M4:N33 AC4:AD33 E34:AJ47">
+    <cfRule type="cellIs" dxfId="55" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="66" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="13" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="65" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="53" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:AB33">
-    <cfRule type="cellIs" dxfId="64" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AJ33">
-    <cfRule type="cellIs" dxfId="63" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AP47">
-    <cfRule type="cellIs" dxfId="62" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="19" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="61" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="49" priority="17" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="60" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="18" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="59" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="12" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30995,114 +30875,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -31199,24 +31079,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -37919,6 +37799,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -37929,65 +37825,49 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="58" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:AO42">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="56" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:AB33">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AJ33">
-    <cfRule type="cellIs" dxfId="54" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AP37 E4:F33 E34:AJ37 AP38:AP42 E43:AP47 M4:N33 AC4:AD33">
-    <cfRule type="cellIs" dxfId="53" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="AK3:AP37 E4:F33 M4:N33 AC4:AD33 E34:AJ37 AP38:AP42 E43:AP47">
+    <cfRule type="cellIs" dxfId="41" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="52" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="51" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38026,114 +37906,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
       <c r="C2" s="143"/>
-      <c r="D2" s="107"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -38230,24 +38110,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -44928,6 +44808,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -44938,105 +44834,89 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="49" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="12" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="48" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:L39">
-    <cfRule type="cellIs" dxfId="47" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42:L42">
-    <cfRule type="cellIs" dxfId="46" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38:T39">
-    <cfRule type="cellIs" dxfId="45" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O42:T42">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O7:T33 O4:AB6">
-    <cfRule type="cellIs" dxfId="43" priority="14" operator="lessThan">
+  <conditionalFormatting sqref="O4:AB6 O7:T33">
+    <cfRule type="cellIs" dxfId="31" priority="14" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W7:AB33">
-    <cfRule type="cellIs" dxfId="42" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="10" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W38:AB39">
-    <cfRule type="cellIs" dxfId="41" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W42:AB42">
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AI39">
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42:AI42">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AJ33">
-    <cfRule type="cellIs" dxfId="37" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AP47 E4:F33 U7:V33 E34:AJ37 E38:F39 M38:N39 U38:V39 AC38:AD39 AJ38:AJ42 E40:AI41 E42:F42 M42:N42 U42:V42 AC42:AD42 E43:AJ47 M4:N33 AC4:AD33">
-    <cfRule type="cellIs" dxfId="36" priority="18" operator="lessThan">
+  <conditionalFormatting sqref="AK3:AP47 E4:F33 M4:N33 AC4:AD33 U7:V33 E34:AJ37 E38:F39 M38:N39 U38:V39 AC38:AD39 AJ38:AJ42 E40:AI41 E42:F42 M42:N42 U42:V42 AC42:AD42 E43:AJ47">
+    <cfRule type="cellIs" dxfId="24" priority="18" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="35" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="16" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="34" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="17" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="33" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45070,114 +44950,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -45274,24 +45154,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -52244,6 +52124,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -52254,60 +52150,44 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:AB33">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AJ33">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AP47 E4:F33 E34:AJ47 M4:N33 AC4:AD33">
-    <cfRule type="cellIs" dxfId="28" priority="8" operator="lessThan">
+  <conditionalFormatting sqref="AK3:AP47 E4:F33 M4:N33 AC4:AD33 E34:AJ47">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="27" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52341,114 +52221,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="117" t="s">
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="129" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="120" t="s">
+      <c r="V1" s="126"/>
+      <c r="W1" s="126"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="126"/>
+      <c r="Z1" s="126"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="121"/>
-      <c r="AF1" s="121"/>
-      <c r="AG1" s="121"/>
-      <c r="AH1" s="121"/>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="122"/>
-      <c r="AK1" s="123" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="129"/>
+      <c r="AF1" s="129"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="129"/>
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="130"/>
+      <c r="AK1" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="AL1" s="125" t="s">
+      <c r="AL1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="AM1" s="132" t="s">
+      <c r="AM1" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="AN1" s="127" t="s">
+      <c r="AN1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="115"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AO1" s="137"/>
+      <c r="AP1" s="139"/>
+      <c r="AR1" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="AS1" s="94" t="s">
+      <c r="AS1" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="AT1" s="96" t="s">
+      <c r="AT1" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="AU1" s="98" t="s">
+      <c r="AU1" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="100" t="s">
+      <c r="AV1" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="AW1" s="94" t="s">
+      <c r="AW1" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" s="96" t="s">
+      <c r="AX1" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="AY1" s="139" t="s">
+      <c r="AY1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="AZ1" s="134" t="s">
+      <c r="AZ1" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="BA1" s="136" t="s">
+      <c r="BA1" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="BB1" s="135" t="s">
+      <c r="BB1" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="138" t="s">
+      <c r="BC1" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:61" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="103"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="107"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="114"/>
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -52545,24 +52425,24 @@
       <c r="AJ2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="126"/>
-      <c r="AM2" s="133"/>
-      <c r="AN2" s="128"/>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="116"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="95"/>
-      <c r="AT2" s="97"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="95"/>
-      <c r="AX2" s="97"/>
-      <c r="AY2" s="140"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="137"/>
-      <c r="BB2" s="135"/>
-      <c r="BC2" s="138"/>
+      <c r="AK2" s="132"/>
+      <c r="AL2" s="134"/>
+      <c r="AM2" s="136"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="138"/>
+      <c r="AP2" s="140"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="100"/>
+      <c r="AU2" s="102"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="106"/>
+      <c r="AX2" s="100"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="95"/>
+      <c r="BA2" s="97"/>
+      <c r="BB2" s="95"/>
+      <c r="BC2" s="98"/>
       <c r="BE2" s="20" t="s">
         <v>0</v>
       </c>
@@ -52781,7 +52661,7 @@
       </c>
       <c r="AH4" s="20"/>
       <c r="AI4" s="20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="45">
@@ -52798,16 +52678,16 @@
       </c>
       <c r="AN4" s="48">
         <f t="shared" ref="AN4:AN47" si="7">SUMIF(AC4:AC4, "&gt;=65") / 4 +SUMIF(AE4:AE4, "&gt;=65") / 4 +SUMIF(AG4:AG4, "&gt;=65") / 4 +SUMIF(AI4:AI4, "&gt;=65") / 4 + SUMIF(AD4:AD4, "&gt;1") / 4 + SUMIF(AF4:AF4, "&gt;1") / 4 + SUMIF(AH4:AH4, "&gt;1") / 4 + SUMIF(AJ4:AJ4, "&gt;1") / 4</f>
-        <v>45.75</v>
+        <v>68.75</v>
       </c>
       <c r="AO4" s="49">
         <f t="shared" ref="AO4:AO47" si="8">AVERAGE(AK4:AN4)</f>
-        <v>45.5</v>
+        <v>51.25</v>
       </c>
       <c r="AP4" s="38"/>
       <c r="AR4" s="55">
         <f t="shared" ref="AR4:AR47" si="9">IF(AO4&lt;70, AO4*0.5, "")</f>
-        <v>22.75</v>
+        <v>25.625</v>
       </c>
       <c r="AS4" s="36"/>
       <c r="AT4" s="57">
@@ -52844,7 +52724,7 @@
       </c>
       <c r="BC4" s="65">
         <f t="shared" ref="BC4:BC47" si="17">IF(AW4&lt;&gt;"", IF(AY4&lt;70, IF(AZ4+BA4&lt;70, AZ4+BA4, ""), ""), IF(AS4&lt;&gt;"", IF(AU4&lt;70, AU4, ""), IF(AO4&lt;70, AO4, "")))</f>
-        <v>45.5</v>
+        <v>51.25</v>
       </c>
       <c r="BE4" s="20">
         <f t="shared" si="0"/>
@@ -52860,11 +52740,11 @@
       </c>
       <c r="BH4" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BI4" s="20">
         <f>AVERAGE(BE4:BH4)</f>
-        <v>45.5</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="5" spans="1:61" x14ac:dyDescent="0.2">
@@ -52938,7 +52818,9 @@
         <v>90</v>
       </c>
       <c r="AH5" s="20"/>
-      <c r="AI5" s="20"/>
+      <c r="AI5" s="20">
+        <v>92</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="45">
         <f t="shared" si="4"/>
@@ -52954,11 +52836,11 @@
       </c>
       <c r="AN5" s="48">
         <f t="shared" si="7"/>
-        <v>67.5</v>
+        <v>90.5</v>
       </c>
       <c r="AO5" s="49">
         <f t="shared" si="8"/>
-        <v>79.625</v>
+        <v>85.375</v>
       </c>
       <c r="AP5" s="38"/>
       <c r="AR5" s="55" t="str">
@@ -52994,7 +52876,7 @@
       <c r="BA5" s="21"/>
       <c r="BB5" s="63">
         <f t="shared" si="16"/>
-        <v>79.625</v>
+        <v>85.375</v>
       </c>
       <c r="BC5" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53014,11 +52896,11 @@
       </c>
       <c r="BH5" s="20">
         <f>SUM(K5+S5+AA5+AI5)/4</f>
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BI5" s="20">
         <f>AVERAGE(BE5:BH5)</f>
-        <v>79.625</v>
+        <v>85.375</v>
       </c>
     </row>
     <row r="6" spans="1:61" x14ac:dyDescent="0.2">
@@ -53092,7 +52974,9 @@
         <v>92</v>
       </c>
       <c r="AH6" s="20"/>
-      <c r="AI6" s="20"/>
+      <c r="AI6" s="20">
+        <v>93</v>
+      </c>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="45">
         <f t="shared" si="4"/>
@@ -53108,11 +52992,11 @@
       </c>
       <c r="AN6" s="48">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>91.25</v>
       </c>
       <c r="AO6" s="49">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>84.8125</v>
       </c>
       <c r="AP6" s="38"/>
       <c r="AR6" s="55" t="str">
@@ -53148,7 +53032,7 @@
       <c r="BA6" s="21"/>
       <c r="BB6" s="63">
         <f t="shared" si="16"/>
-        <v>79</v>
+        <v>84.8125</v>
       </c>
       <c r="BC6" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53168,11 +53052,11 @@
       </c>
       <c r="BH6" s="20">
         <f t="shared" ref="BH6:BH47" si="21">SUM(K6+S6+AA6+AI6)/4</f>
-        <v>45.5</v>
+        <v>68.75</v>
       </c>
       <c r="BI6" s="20">
         <f t="shared" ref="BI6:BI47" si="22">AVERAGE(BE6:BH6)</f>
-        <v>79</v>
+        <v>84.8125</v>
       </c>
     </row>
     <row r="7" spans="1:61" x14ac:dyDescent="0.2">
@@ -53246,7 +53130,9 @@
         <v>90</v>
       </c>
       <c r="AH7" s="20"/>
-      <c r="AI7" s="20"/>
+      <c r="AI7" s="20">
+        <v>92</v>
+      </c>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="45">
         <f t="shared" si="4"/>
@@ -53262,11 +53148,11 @@
       </c>
       <c r="AN7" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90.75</v>
       </c>
       <c r="AO7" s="49">
         <f t="shared" si="8"/>
-        <v>79.0625</v>
+        <v>84.8125</v>
       </c>
       <c r="AP7" s="38"/>
       <c r="AR7" s="55" t="str">
@@ -53302,7 +53188,7 @@
       <c r="BA7" s="21"/>
       <c r="BB7" s="63">
         <f t="shared" si="16"/>
-        <v>79.0625</v>
+        <v>84.8125</v>
       </c>
       <c r="BC7" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53322,11 +53208,11 @@
       </c>
       <c r="BH7" s="20">
         <f t="shared" si="21"/>
-        <v>44.75</v>
+        <v>67.75</v>
       </c>
       <c r="BI7" s="20">
         <f t="shared" si="22"/>
-        <v>79.0625</v>
+        <v>84.8125</v>
       </c>
     </row>
     <row r="8" spans="1:61" x14ac:dyDescent="0.2">
@@ -53400,7 +53286,9 @@
         <v>88</v>
       </c>
       <c r="AH8" s="20"/>
-      <c r="AI8" s="20"/>
+      <c r="AI8" s="20">
+        <v>80</v>
+      </c>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="45">
         <f t="shared" si="4"/>
@@ -53416,11 +53304,11 @@
       </c>
       <c r="AN8" s="48">
         <f t="shared" si="7"/>
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO8" s="49">
         <f t="shared" si="8"/>
-        <v>71.375</v>
+        <v>76.375</v>
       </c>
       <c r="AP8" s="38"/>
       <c r="AR8" s="55" t="str">
@@ -53456,7 +53344,7 @@
       <c r="BA8" s="21"/>
       <c r="BB8" s="63">
         <f t="shared" si="16"/>
-        <v>71.375</v>
+        <v>76.375</v>
       </c>
       <c r="BC8" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53476,11 +53364,11 @@
       </c>
       <c r="BH8" s="20">
         <f t="shared" si="21"/>
-        <v>39.25</v>
+        <v>59.25</v>
       </c>
       <c r="BI8" s="20">
         <f t="shared" si="22"/>
-        <v>71.375</v>
+        <v>76.375</v>
       </c>
     </row>
     <row r="9" spans="1:61" x14ac:dyDescent="0.2">
@@ -53554,7 +53442,9 @@
         <v>90</v>
       </c>
       <c r="AH9" s="20"/>
-      <c r="AI9" s="20"/>
+      <c r="AI9" s="20">
+        <v>89</v>
+      </c>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="45">
         <f t="shared" si="4"/>
@@ -53570,11 +53460,11 @@
       </c>
       <c r="AN9" s="48">
         <f t="shared" si="7"/>
-        <v>66.5</v>
+        <v>88.75</v>
       </c>
       <c r="AO9" s="49">
         <f t="shared" si="8"/>
-        <v>78.75</v>
+        <v>84.3125</v>
       </c>
       <c r="AP9" s="38"/>
       <c r="AR9" s="55" t="str">
@@ -53610,7 +53500,7 @@
       <c r="BA9" s="21"/>
       <c r="BB9" s="63">
         <f t="shared" si="16"/>
-        <v>78.75</v>
+        <v>84.3125</v>
       </c>
       <c r="BC9" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53630,11 +53520,11 @@
       </c>
       <c r="BH9" s="20">
         <f t="shared" si="21"/>
-        <v>46</v>
+        <v>68.25</v>
       </c>
       <c r="BI9" s="20">
         <f t="shared" si="22"/>
-        <v>78.75</v>
+        <v>84.3125</v>
       </c>
     </row>
     <row r="10" spans="1:61" x14ac:dyDescent="0.2">
@@ -53708,7 +53598,9 @@
         <v>85</v>
       </c>
       <c r="AH10" s="20"/>
-      <c r="AI10" s="20"/>
+      <c r="AI10" s="20">
+        <v>75</v>
+      </c>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="45">
         <f t="shared" si="4"/>
@@ -53724,16 +53616,16 @@
       </c>
       <c r="AN10" s="48">
         <f t="shared" si="7"/>
-        <v>60.25</v>
+        <v>79</v>
       </c>
       <c r="AO10" s="49">
         <f t="shared" si="8"/>
-        <v>69.0625</v>
+        <v>73.75</v>
       </c>
       <c r="AP10" s="38"/>
-      <c r="AR10" s="55">
+      <c r="AR10" s="55" t="str">
         <f t="shared" si="9"/>
-        <v>34.53125</v>
+        <v/>
       </c>
       <c r="AS10" s="36"/>
       <c r="AT10" s="57">
@@ -53762,13 +53654,13 @@
         <v/>
       </c>
       <c r="BA10" s="21"/>
-      <c r="BB10" s="63" t="str">
+      <c r="BB10" s="63">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="BC10" s="65">
+        <v>73.75</v>
+      </c>
+      <c r="BC10" s="65" t="str">
         <f t="shared" si="17"/>
-        <v>69.0625</v>
+        <v/>
       </c>
       <c r="BE10" s="20">
         <f t="shared" si="18"/>
@@ -53784,11 +53676,11 @@
       </c>
       <c r="BH10" s="20">
         <f t="shared" si="21"/>
-        <v>39.75</v>
+        <v>58.5</v>
       </c>
       <c r="BI10" s="20">
         <f t="shared" si="22"/>
-        <v>69.0625</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="11" spans="1:61" x14ac:dyDescent="0.2">
@@ -53862,7 +53754,9 @@
         <v>90</v>
       </c>
       <c r="AH11" s="20"/>
-      <c r="AI11" s="20"/>
+      <c r="AI11" s="20">
+        <v>87</v>
+      </c>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="45">
         <f t="shared" si="4"/>
@@ -53878,11 +53772,11 @@
       </c>
       <c r="AN11" s="48">
         <f t="shared" si="7"/>
-        <v>67.5</v>
+        <v>89.25</v>
       </c>
       <c r="AO11" s="49">
         <f t="shared" si="8"/>
-        <v>78.6875</v>
+        <v>84.125</v>
       </c>
       <c r="AP11" s="38"/>
       <c r="AR11" s="55" t="str">
@@ -53918,7 +53812,7 @@
       <c r="BA11" s="21"/>
       <c r="BB11" s="63">
         <f t="shared" si="16"/>
-        <v>78.6875</v>
+        <v>84.125</v>
       </c>
       <c r="BC11" s="65" t="str">
         <f t="shared" si="17"/>
@@ -53938,11 +53832,11 @@
       </c>
       <c r="BH11" s="20">
         <f t="shared" si="21"/>
-        <v>45.5</v>
+        <v>67.25</v>
       </c>
       <c r="BI11" s="20">
         <f t="shared" si="22"/>
-        <v>78.6875</v>
+        <v>84.125</v>
       </c>
     </row>
     <row r="12" spans="1:61" x14ac:dyDescent="0.2">
@@ -54144,7 +54038,9 @@
         <v>79</v>
       </c>
       <c r="AH13" s="20"/>
-      <c r="AI13" s="20"/>
+      <c r="AI13" s="20">
+        <v>76</v>
+      </c>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="45">
         <f t="shared" si="4"/>
@@ -54160,11 +54056,11 @@
       </c>
       <c r="AN13" s="48">
         <f t="shared" si="7"/>
-        <v>58.5</v>
+        <v>77.5</v>
       </c>
       <c r="AO13" s="49">
         <f t="shared" si="8"/>
-        <v>72.0625</v>
+        <v>76.8125</v>
       </c>
       <c r="AP13" s="38"/>
       <c r="AR13" s="55" t="str">
@@ -54200,7 +54096,7 @@
       <c r="BA13" s="21"/>
       <c r="BB13" s="63">
         <f t="shared" si="16"/>
-        <v>72.0625</v>
+        <v>76.8125</v>
       </c>
       <c r="BC13" s="65" t="str">
         <f t="shared" si="17"/>
@@ -54220,11 +54116,11 @@
       </c>
       <c r="BH13" s="20">
         <f t="shared" si="21"/>
-        <v>57.5</v>
+        <v>76.5</v>
       </c>
       <c r="BI13" s="20">
         <f t="shared" si="22"/>
-        <v>72.0625</v>
+        <v>76.8125</v>
       </c>
     </row>
     <row r="14" spans="1:61" x14ac:dyDescent="0.2">
@@ -54300,7 +54196,9 @@
         <v>90</v>
       </c>
       <c r="AH14" s="20"/>
-      <c r="AI14" s="20"/>
+      <c r="AI14" s="20">
+        <v>91</v>
+      </c>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="45">
         <f t="shared" si="4"/>
@@ -54316,11 +54214,11 @@
       </c>
       <c r="AN14" s="48">
         <f t="shared" si="7"/>
-        <v>67.25</v>
+        <v>90</v>
       </c>
       <c r="AO14" s="49">
         <f t="shared" si="8"/>
-        <v>84.125</v>
+        <v>89.8125</v>
       </c>
       <c r="AP14" s="38"/>
       <c r="AR14" s="55" t="str">
@@ -54356,7 +54254,7 @@
       <c r="BA14" s="21"/>
       <c r="BB14" s="63">
         <f t="shared" si="16"/>
-        <v>84.125</v>
+        <v>89.8125</v>
       </c>
       <c r="BC14" s="65" t="str">
         <f t="shared" si="17"/>
@@ -54376,11 +54274,11 @@
       </c>
       <c r="BH14" s="20">
         <f t="shared" si="21"/>
-        <v>67</v>
+        <v>89.75</v>
       </c>
       <c r="BI14" s="20">
         <f t="shared" si="22"/>
-        <v>84.125</v>
+        <v>89.8125</v>
       </c>
     </row>
     <row r="15" spans="1:61" x14ac:dyDescent="0.2">
@@ -54442,7 +54340,9 @@
       <c r="AF15" s="20"/>
       <c r="AG15" s="20"/>
       <c r="AH15" s="20"/>
-      <c r="AI15" s="20"/>
+      <c r="AI15" s="20">
+        <v>88</v>
+      </c>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="45">
         <f t="shared" si="4"/>
@@ -54458,16 +54358,16 @@
       </c>
       <c r="AN15" s="48">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO15" s="49">
         <f t="shared" si="8"/>
-        <v>43.875</v>
+        <v>49.375</v>
       </c>
       <c r="AP15" s="38"/>
       <c r="AR15" s="55">
         <f t="shared" si="9"/>
-        <v>21.9375</v>
+        <v>24.6875</v>
       </c>
       <c r="AS15" s="20"/>
       <c r="AT15" s="57">
@@ -54502,7 +54402,7 @@
       </c>
       <c r="BC15" s="65">
         <f t="shared" si="17"/>
-        <v>43.875</v>
+        <v>49.375</v>
       </c>
       <c r="BE15" s="20">
         <f t="shared" si="18"/>
@@ -54518,11 +54418,11 @@
       </c>
       <c r="BH15" s="20">
         <f t="shared" si="21"/>
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="BI15" s="20">
         <f t="shared" si="22"/>
-        <v>43.875</v>
+        <v>49.375</v>
       </c>
     </row>
     <row r="16" spans="1:61" x14ac:dyDescent="0.2">
@@ -54724,7 +54624,9 @@
         <v>88</v>
       </c>
       <c r="AH17" s="20"/>
-      <c r="AI17" s="20"/>
+      <c r="AI17" s="20">
+        <v>79</v>
+      </c>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="45">
         <f t="shared" si="4"/>
@@ -54740,11 +54642,11 @@
       </c>
       <c r="AN17" s="48">
         <f t="shared" si="7"/>
-        <v>63.5</v>
+        <v>83.25</v>
       </c>
       <c r="AO17" s="49">
         <f t="shared" si="8"/>
-        <v>78.5</v>
+        <v>83.4375</v>
       </c>
       <c r="AP17" s="38"/>
       <c r="AR17" s="55" t="str">
@@ -54780,7 +54682,7 @@
       <c r="BA17" s="21"/>
       <c r="BB17" s="63">
         <f t="shared" si="16"/>
-        <v>78.5</v>
+        <v>83.4375</v>
       </c>
       <c r="BC17" s="65" t="str">
         <f t="shared" si="17"/>
@@ -54800,11 +54702,11 @@
       </c>
       <c r="BH17" s="20">
         <f t="shared" si="21"/>
-        <v>64.5</v>
+        <v>84.25</v>
       </c>
       <c r="BI17" s="20">
         <f t="shared" si="22"/>
-        <v>78.5</v>
+        <v>83.4375</v>
       </c>
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.2">
@@ -54880,7 +54782,9 @@
         <v>89</v>
       </c>
       <c r="AH18" s="20"/>
-      <c r="AI18" s="20"/>
+      <c r="AI18" s="20">
+        <v>89</v>
+      </c>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="45">
         <f t="shared" si="4"/>
@@ -54896,11 +54800,11 @@
       </c>
       <c r="AN18" s="48">
         <f t="shared" si="7"/>
-        <v>66.75</v>
+        <v>89</v>
       </c>
       <c r="AO18" s="49">
         <f t="shared" si="8"/>
-        <v>83.8125</v>
+        <v>89.375</v>
       </c>
       <c r="AP18" s="38"/>
       <c r="AR18" s="55" t="str">
@@ -54936,7 +54840,7 @@
       <c r="BA18" s="21"/>
       <c r="BB18" s="63">
         <f t="shared" si="16"/>
-        <v>83.8125</v>
+        <v>89.375</v>
       </c>
       <c r="BC18" s="65" t="str">
         <f t="shared" si="17"/>
@@ -54956,11 +54860,11 @@
       </c>
       <c r="BH18" s="20">
         <f t="shared" si="21"/>
-        <v>68.25</v>
+        <v>90.5</v>
       </c>
       <c r="BI18" s="20">
         <f t="shared" si="22"/>
-        <v>83.8125</v>
+        <v>89.375</v>
       </c>
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.2">
@@ -55036,7 +54940,9 @@
         <v>89</v>
       </c>
       <c r="AH19" s="20"/>
-      <c r="AI19" s="20"/>
+      <c r="AI19" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="45">
         <f t="shared" si="4"/>
@@ -55052,11 +54958,11 @@
       </c>
       <c r="AN19" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90.25</v>
       </c>
       <c r="AO19" s="49">
         <f t="shared" si="8"/>
-        <v>84.625</v>
+        <v>90.25</v>
       </c>
       <c r="AP19" s="38"/>
       <c r="AR19" s="55" t="str">
@@ -55092,7 +54998,7 @@
       <c r="BA19" s="21"/>
       <c r="BB19" s="63">
         <f t="shared" si="16"/>
-        <v>84.625</v>
+        <v>90.25</v>
       </c>
       <c r="BC19" s="65" t="str">
         <f t="shared" si="17"/>
@@ -55112,11 +55018,11 @@
       </c>
       <c r="BH19" s="20">
         <f t="shared" si="21"/>
-        <v>69</v>
+        <v>91.5</v>
       </c>
       <c r="BI19" s="20">
         <f t="shared" si="22"/>
-        <v>84.625</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.2">
@@ -55318,7 +55224,9 @@
         <v>90</v>
       </c>
       <c r="AH21" s="20"/>
-      <c r="AI21" s="20"/>
+      <c r="AI21" s="20">
+        <v>92</v>
+      </c>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="45">
         <f t="shared" si="4"/>
@@ -55334,11 +55242,11 @@
       </c>
       <c r="AN21" s="48">
         <f t="shared" si="7"/>
-        <v>67.25</v>
+        <v>90.25</v>
       </c>
       <c r="AO21" s="49">
         <f t="shared" si="8"/>
-        <v>84.5</v>
+        <v>90.25</v>
       </c>
       <c r="AP21" s="38"/>
       <c r="AR21" s="55" t="str">
@@ -55374,7 +55282,7 @@
       <c r="BA21" s="21"/>
       <c r="BB21" s="63">
         <f t="shared" si="16"/>
-        <v>84.5</v>
+        <v>90.25</v>
       </c>
       <c r="BC21" s="65" t="str">
         <f t="shared" si="17"/>
@@ -55394,11 +55302,11 @@
       </c>
       <c r="BH21" s="20">
         <f t="shared" si="21"/>
-        <v>68.25</v>
+        <v>91.25</v>
       </c>
       <c r="BI21" s="20">
         <f t="shared" si="22"/>
-        <v>84.5</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.2">
@@ -55474,7 +55382,9 @@
         <v>87</v>
       </c>
       <c r="AH22" s="20"/>
-      <c r="AI22" s="20"/>
+      <c r="AI22" s="20">
+        <v>87</v>
+      </c>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="45">
         <f t="shared" si="4"/>
@@ -55490,11 +55400,11 @@
       </c>
       <c r="AN22" s="48">
         <f t="shared" si="7"/>
-        <v>65.5</v>
+        <v>87.25</v>
       </c>
       <c r="AO22" s="49">
         <f t="shared" si="8"/>
-        <v>83.1875</v>
+        <v>88.625</v>
       </c>
       <c r="AP22" s="38"/>
       <c r="AR22" s="55" t="str">
@@ -55530,7 +55440,7 @@
       <c r="BA22" s="21"/>
       <c r="BB22" s="63">
         <f t="shared" si="16"/>
-        <v>83.1875</v>
+        <v>88.625</v>
       </c>
       <c r="BC22" s="65" t="str">
         <f t="shared" si="17"/>
@@ -55550,11 +55460,11 @@
       </c>
       <c r="BH22" s="20">
         <f t="shared" si="21"/>
-        <v>68</v>
+        <v>89.75</v>
       </c>
       <c r="BI22" s="20">
         <f t="shared" si="22"/>
-        <v>83.1875</v>
+        <v>88.625</v>
       </c>
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.2">
@@ -55756,7 +55666,9 @@
         <v>87</v>
       </c>
       <c r="AH24" s="20"/>
-      <c r="AI24" s="20"/>
+      <c r="AI24" s="20">
+        <v>86</v>
+      </c>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="45">
         <f t="shared" si="4"/>
@@ -55772,11 +55684,11 @@
       </c>
       <c r="AN24" s="48">
         <f t="shared" si="7"/>
-        <v>64.25</v>
+        <v>85.75</v>
       </c>
       <c r="AO24" s="49">
         <f t="shared" si="8"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
       <c r="AP24" s="38"/>
       <c r="AR24" s="55" t="str">
@@ -55812,7 +55724,7 @@
       <c r="BA24" s="21"/>
       <c r="BB24" s="63">
         <f t="shared" si="16"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
       <c r="BC24" s="65" t="str">
         <f t="shared" si="17"/>
@@ -55832,11 +55744,11 @@
       </c>
       <c r="BH24" s="20">
         <f t="shared" si="21"/>
-        <v>65.5</v>
+        <v>87</v>
       </c>
       <c r="BI24" s="20">
         <f t="shared" si="22"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.2">
@@ -56046,7 +55958,9 @@
         <v>79</v>
       </c>
       <c r="AH26" s="20"/>
-      <c r="AI26" s="20"/>
+      <c r="AI26" s="20">
+        <v>76</v>
+      </c>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="45">
         <f t="shared" si="4"/>
@@ -56062,11 +55976,11 @@
       </c>
       <c r="AN26" s="48">
         <f t="shared" si="7"/>
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="AO26" s="49">
         <f t="shared" si="8"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
       <c r="AP26" s="38"/>
       <c r="AR26" s="55" t="str">
@@ -56102,7 +56016,7 @@
       <c r="BA26" s="21"/>
       <c r="BB26" s="63">
         <f t="shared" si="16"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
       <c r="BC26" s="65" t="str">
         <f t="shared" si="17"/>
@@ -56122,11 +56036,11 @@
       </c>
       <c r="BH26" s="20">
         <f t="shared" si="21"/>
-        <v>59.25</v>
+        <v>78.25</v>
       </c>
       <c r="BI26" s="20">
         <f t="shared" si="22"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.2">
@@ -56202,7 +56116,9 @@
         <v>86</v>
       </c>
       <c r="AH27" s="20"/>
-      <c r="AI27" s="20"/>
+      <c r="AI27" s="20">
+        <v>87</v>
+      </c>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="45">
         <f t="shared" si="4"/>
@@ -56218,11 +56134,11 @@
       </c>
       <c r="AN27" s="48">
         <f t="shared" si="7"/>
-        <v>64.5</v>
+        <v>86.25</v>
       </c>
       <c r="AO27" s="49">
         <f t="shared" si="8"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
       <c r="AP27" s="38"/>
       <c r="AR27" s="55" t="str">
@@ -56258,7 +56174,7 @@
       <c r="BA27" s="21"/>
       <c r="BB27" s="63">
         <f t="shared" si="16"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
       <c r="BC27" s="65" t="str">
         <f t="shared" si="17"/>
@@ -56278,11 +56194,11 @@
       </c>
       <c r="BH27" s="20">
         <f t="shared" si="21"/>
-        <v>62.75</v>
+        <v>84.5</v>
       </c>
       <c r="BI27" s="20">
         <f t="shared" si="22"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.2">
@@ -56358,7 +56274,9 @@
         <v>90</v>
       </c>
       <c r="AH28" s="20"/>
-      <c r="AI28" s="20"/>
+      <c r="AI28" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="45">
         <f t="shared" si="4"/>
@@ -56374,11 +56292,11 @@
       </c>
       <c r="AN28" s="48">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>90.5</v>
       </c>
       <c r="AO28" s="49">
         <f t="shared" si="8"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="AP28" s="38"/>
       <c r="AR28" s="55" t="str">
@@ -56414,7 +56332,7 @@
       <c r="BA28" s="21"/>
       <c r="BB28" s="63">
         <f t="shared" si="16"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="BC28" s="65" t="str">
         <f t="shared" si="17"/>
@@ -56434,11 +56352,11 @@
       </c>
       <c r="BH28" s="20">
         <f t="shared" si="21"/>
-        <v>68.25</v>
+        <v>90.75</v>
       </c>
       <c r="BI28" s="20">
         <f t="shared" si="22"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.2">
@@ -56514,7 +56432,9 @@
         <v>90</v>
       </c>
       <c r="AH29" s="20"/>
-      <c r="AI29" s="20"/>
+      <c r="AI29" s="20">
+        <v>89</v>
+      </c>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="45">
         <f t="shared" si="4"/>
@@ -56530,11 +56450,11 @@
       </c>
       <c r="AN29" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90</v>
       </c>
       <c r="AO29" s="49">
         <f t="shared" si="8"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
       <c r="AP29" s="38"/>
       <c r="AR29" s="55" t="str">
@@ -56570,7 +56490,7 @@
       <c r="BA29" s="21"/>
       <c r="BB29" s="63">
         <f t="shared" si="16"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
       <c r="BC29" s="65" t="str">
         <f t="shared" si="17"/>
@@ -56590,11 +56510,11 @@
       </c>
       <c r="BH29" s="20">
         <f t="shared" si="21"/>
-        <v>68</v>
+        <v>90.25</v>
       </c>
       <c r="BI29" s="20">
         <f t="shared" si="22"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.2">
@@ -56670,7 +56590,9 @@
         <v>90</v>
       </c>
       <c r="AH30" s="20"/>
-      <c r="AI30" s="20"/>
+      <c r="AI30" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="45">
         <f t="shared" si="4"/>
@@ -56686,11 +56608,11 @@
       </c>
       <c r="AN30" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90.25</v>
       </c>
       <c r="AO30" s="49">
         <f t="shared" si="8"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="AP30" s="38"/>
       <c r="AR30" s="55" t="str">
@@ -56726,7 +56648,7 @@
       <c r="BA30" s="21"/>
       <c r="BB30" s="63">
         <f t="shared" si="16"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="BC30" s="65" t="str">
         <f t="shared" si="17"/>
@@ -56746,11 +56668,11 @@
       </c>
       <c r="BH30" s="20">
         <f t="shared" si="21"/>
-        <v>67</v>
+        <v>89.5</v>
       </c>
       <c r="BI30" s="20">
         <f t="shared" si="22"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.2">
@@ -56952,7 +56874,9 @@
         <v>85</v>
       </c>
       <c r="AH32" s="20"/>
-      <c r="AI32" s="20"/>
+      <c r="AI32" s="20">
+        <v>88</v>
+      </c>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="45">
         <f t="shared" si="4"/>
@@ -56968,11 +56892,11 @@
       </c>
       <c r="AN32" s="48">
         <f t="shared" si="7"/>
-        <v>64.75</v>
+        <v>86.75</v>
       </c>
       <c r="AO32" s="49">
         <f t="shared" si="8"/>
-        <v>81.5625</v>
+        <v>87.0625</v>
       </c>
       <c r="AP32" s="38"/>
       <c r="AR32" s="55" t="str">
@@ -57008,7 +56932,7 @@
       <c r="BA32" s="21"/>
       <c r="BB32" s="63">
         <f t="shared" si="16"/>
-        <v>81.5625</v>
+        <v>87.0625</v>
       </c>
       <c r="BC32" s="65" t="str">
         <f t="shared" si="17"/>
@@ -57028,11 +56952,11 @@
       </c>
       <c r="BH32" s="20">
         <f t="shared" si="21"/>
-        <v>65.5</v>
+        <v>87.5</v>
       </c>
       <c r="BI32" s="20">
         <f t="shared" si="22"/>
-        <v>81.5625</v>
+        <v>87.0625</v>
       </c>
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.2">
@@ -57108,7 +57032,9 @@
         <v>89</v>
       </c>
       <c r="AH33" s="20"/>
-      <c r="AI33" s="20"/>
+      <c r="AI33" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="45">
         <f t="shared" si="4"/>
@@ -57124,11 +57050,11 @@
       </c>
       <c r="AN33" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90.25</v>
       </c>
       <c r="AO33" s="49">
         <f t="shared" si="8"/>
-        <v>84.5625</v>
+        <v>90.1875</v>
       </c>
       <c r="AP33" s="38"/>
       <c r="AR33" s="55" t="str">
@@ -57164,7 +57090,7 @@
       <c r="BA33" s="21"/>
       <c r="BB33" s="63">
         <f t="shared" si="16"/>
-        <v>84.5625</v>
+        <v>90.1875</v>
       </c>
       <c r="BC33" s="65" t="str">
         <f t="shared" si="17"/>
@@ -57184,11 +57110,11 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="21"/>
-        <v>67</v>
+        <v>89.5</v>
       </c>
       <c r="BI33" s="20">
         <f t="shared" si="22"/>
-        <v>84.5625</v>
+        <v>90.1875</v>
       </c>
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.2">
@@ -57250,7 +57176,9 @@
       <c r="AF34" s="20"/>
       <c r="AG34" s="20"/>
       <c r="AH34" s="20"/>
-      <c r="AI34" s="20"/>
+      <c r="AI34" s="20">
+        <v>80</v>
+      </c>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="45">
         <f t="shared" si="4"/>
@@ -57266,16 +57194,16 @@
       </c>
       <c r="AN34" s="48">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO34" s="49">
         <f t="shared" si="8"/>
-        <v>37.9375</v>
+        <v>42.9375</v>
       </c>
       <c r="AP34" s="38"/>
       <c r="AR34" s="55">
         <f t="shared" si="9"/>
-        <v>18.96875</v>
+        <v>21.46875</v>
       </c>
       <c r="AS34" s="20"/>
       <c r="AT34" s="57">
@@ -57310,7 +57238,7 @@
       </c>
       <c r="BC34" s="65">
         <f t="shared" si="17"/>
-        <v>37.9375</v>
+        <v>42.9375</v>
       </c>
       <c r="BE34" s="20">
         <f t="shared" si="18"/>
@@ -57326,11 +57254,11 @@
       </c>
       <c r="BH34" s="20">
         <f t="shared" si="21"/>
-        <v>38.25</v>
+        <v>58.25</v>
       </c>
       <c r="BI34" s="20">
         <f t="shared" si="22"/>
-        <v>37.9375</v>
+        <v>42.9375</v>
       </c>
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.2">
@@ -57406,7 +57334,9 @@
         <v>81</v>
       </c>
       <c r="AH35" s="20"/>
-      <c r="AI35" s="20"/>
+      <c r="AI35" s="20">
+        <v>85</v>
+      </c>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="45">
         <f t="shared" si="4"/>
@@ -57422,11 +57352,11 @@
       </c>
       <c r="AN35" s="48">
         <f t="shared" si="7"/>
-        <v>62.75</v>
+        <v>84</v>
       </c>
       <c r="AO35" s="49">
         <f t="shared" si="8"/>
-        <v>80.125</v>
+        <v>85.4375</v>
       </c>
       <c r="AP35" s="38"/>
       <c r="AR35" s="55" t="str">
@@ -57462,7 +57392,7 @@
       <c r="BA35" s="21"/>
       <c r="BB35" s="63">
         <f t="shared" si="16"/>
-        <v>80.125</v>
+        <v>85.4375</v>
       </c>
       <c r="BC35" s="65" t="str">
         <f t="shared" si="17"/>
@@ -57482,11 +57412,11 @@
       </c>
       <c r="BH35" s="20">
         <f t="shared" si="21"/>
-        <v>64.5</v>
+        <v>85.75</v>
       </c>
       <c r="BI35" s="20">
         <f t="shared" si="22"/>
-        <v>80.125</v>
+        <v>85.4375</v>
       </c>
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.2">
@@ -57548,7 +57478,9 @@
       <c r="AF36" s="20"/>
       <c r="AG36" s="20"/>
       <c r="AH36" s="20"/>
-      <c r="AI36" s="20"/>
+      <c r="AI36" s="20">
+        <v>88</v>
+      </c>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="45">
         <f t="shared" si="4"/>
@@ -57564,16 +57496,16 @@
       </c>
       <c r="AN36" s="48">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO36" s="49">
         <f t="shared" si="8"/>
-        <v>44.75</v>
+        <v>50.25</v>
       </c>
       <c r="AP36" s="38"/>
       <c r="AR36" s="55">
         <f t="shared" si="9"/>
-        <v>22.375</v>
+        <v>25.125</v>
       </c>
       <c r="AS36" s="20"/>
       <c r="AT36" s="57">
@@ -57608,7 +57540,7 @@
       </c>
       <c r="BC36" s="65">
         <f t="shared" si="17"/>
-        <v>44.75</v>
+        <v>50.25</v>
       </c>
       <c r="BE36" s="20">
         <f t="shared" si="18"/>
@@ -57624,11 +57556,11 @@
       </c>
       <c r="BH36" s="20">
         <f t="shared" si="21"/>
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="BI36" s="20">
         <f t="shared" si="22"/>
-        <v>44.75</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.2">
@@ -57702,7 +57634,9 @@
         <v>90</v>
       </c>
       <c r="AH37" s="20"/>
-      <c r="AI37" s="20"/>
+      <c r="AI37" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="45">
         <f t="shared" si="4"/>
@@ -57718,11 +57652,11 @@
       </c>
       <c r="AN37" s="48">
         <f t="shared" si="7"/>
-        <v>45.5</v>
+        <v>68</v>
       </c>
       <c r="AO37" s="49">
         <f t="shared" si="8"/>
-        <v>78.3125</v>
+        <v>83.9375</v>
       </c>
       <c r="AP37" s="38"/>
       <c r="AR37" s="55" t="str">
@@ -57758,7 +57692,7 @@
       <c r="BA37" s="21"/>
       <c r="BB37" s="63">
         <f t="shared" si="16"/>
-        <v>78.3125</v>
+        <v>83.9375</v>
       </c>
       <c r="BC37" s="65" t="str">
         <f t="shared" si="17"/>
@@ -57778,11 +57712,11 @@
       </c>
       <c r="BH37" s="20">
         <f t="shared" si="21"/>
-        <v>66.5</v>
+        <v>89</v>
       </c>
       <c r="BI37" s="20">
         <f t="shared" si="22"/>
-        <v>78.3125</v>
+        <v>83.9375</v>
       </c>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.2">
@@ -57858,7 +57792,9 @@
         <v>87</v>
       </c>
       <c r="AH38" s="20"/>
-      <c r="AI38" s="20"/>
+      <c r="AI38" s="20">
+        <v>86</v>
+      </c>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="45">
         <f t="shared" si="4"/>
@@ -57874,11 +57810,11 @@
       </c>
       <c r="AN38" s="48">
         <f t="shared" si="7"/>
-        <v>64.25</v>
+        <v>85.75</v>
       </c>
       <c r="AO38" s="49">
         <f t="shared" si="8"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
       <c r="AP38" s="38"/>
       <c r="AR38" s="55" t="str">
@@ -57914,7 +57850,7 @@
       <c r="BA38" s="21"/>
       <c r="BB38" s="63">
         <f t="shared" si="16"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
       <c r="BC38" s="65" t="str">
         <f t="shared" si="17"/>
@@ -57934,11 +57870,11 @@
       </c>
       <c r="BH38" s="20">
         <f t="shared" si="21"/>
-        <v>65.5</v>
+        <v>87</v>
       </c>
       <c r="BI38" s="20">
         <f t="shared" si="22"/>
-        <v>81.1875</v>
+        <v>86.5625</v>
       </c>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.2">
@@ -58148,7 +58084,9 @@
         <v>79</v>
       </c>
       <c r="AH40" s="20"/>
-      <c r="AI40" s="20"/>
+      <c r="AI40" s="20">
+        <v>76</v>
+      </c>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="45">
         <f t="shared" si="4"/>
@@ -58164,11 +58102,11 @@
       </c>
       <c r="AN40" s="48">
         <f t="shared" si="7"/>
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="AO40" s="49">
         <f t="shared" si="8"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
       <c r="AP40" s="38"/>
       <c r="AR40" s="55" t="str">
@@ -58204,7 +58142,7 @@
       <c r="BA40" s="21"/>
       <c r="BB40" s="63">
         <f t="shared" si="16"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
       <c r="BC40" s="65" t="str">
         <f t="shared" si="17"/>
@@ -58224,11 +58162,11 @@
       </c>
       <c r="BH40" s="20">
         <f t="shared" si="21"/>
-        <v>59.25</v>
+        <v>78.25</v>
       </c>
       <c r="BI40" s="20">
         <f t="shared" si="22"/>
-        <v>72.875</v>
+        <v>77.625</v>
       </c>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.2">
@@ -58304,7 +58242,9 @@
         <v>86</v>
       </c>
       <c r="AH41" s="20"/>
-      <c r="AI41" s="20"/>
+      <c r="AI41" s="20">
+        <v>87</v>
+      </c>
       <c r="AJ41" s="3"/>
       <c r="AK41" s="45">
         <f t="shared" si="4"/>
@@ -58320,11 +58260,11 @@
       </c>
       <c r="AN41" s="48">
         <f t="shared" si="7"/>
-        <v>64.5</v>
+        <v>86.25</v>
       </c>
       <c r="AO41" s="49">
         <f t="shared" si="8"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
       <c r="AP41" s="38"/>
       <c r="AR41" s="55" t="str">
@@ -58360,7 +58300,7 @@
       <c r="BA41" s="21"/>
       <c r="BB41" s="63">
         <f t="shared" si="16"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
       <c r="BC41" s="65" t="str">
         <f t="shared" si="17"/>
@@ -58380,11 +58320,11 @@
       </c>
       <c r="BH41" s="20">
         <f t="shared" si="21"/>
-        <v>62.75</v>
+        <v>84.5</v>
       </c>
       <c r="BI41" s="20">
         <f t="shared" si="22"/>
-        <v>79.9375</v>
+        <v>85.375</v>
       </c>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.2">
@@ -58460,7 +58400,9 @@
         <v>90</v>
       </c>
       <c r="AH42" s="20"/>
-      <c r="AI42" s="20"/>
+      <c r="AI42" s="20">
+        <v>90</v>
+      </c>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="45">
         <f t="shared" si="4"/>
@@ -58476,11 +58418,11 @@
       </c>
       <c r="AN42" s="48">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>90.5</v>
       </c>
       <c r="AO42" s="49">
         <f t="shared" si="8"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="AP42" s="38"/>
       <c r="AR42" s="55" t="str">
@@ -58516,7 +58458,7 @@
       <c r="BA42" s="21"/>
       <c r="BB42" s="63">
         <f t="shared" si="16"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
       <c r="BC42" s="65" t="str">
         <f t="shared" si="17"/>
@@ -58536,11 +58478,11 @@
       </c>
       <c r="BH42" s="20">
         <f t="shared" si="21"/>
-        <v>68.25</v>
+        <v>90.75</v>
       </c>
       <c r="BI42" s="20">
         <f t="shared" si="22"/>
-        <v>84.25</v>
+        <v>89.875</v>
       </c>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.2">
@@ -58612,7 +58554,9 @@
         <v>90</v>
       </c>
       <c r="AH43" s="20"/>
-      <c r="AI43" s="20"/>
+      <c r="AI43" s="20">
+        <v>89</v>
+      </c>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="45">
         <f t="shared" si="4"/>
@@ -58628,11 +58572,11 @@
       </c>
       <c r="AN43" s="48">
         <f t="shared" si="7"/>
-        <v>67.75</v>
+        <v>90</v>
       </c>
       <c r="AO43" s="49">
         <f t="shared" si="8"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
       <c r="AP43" s="38"/>
       <c r="AR43" s="55" t="str">
@@ -58668,7 +58612,7 @@
       <c r="BA43" s="21"/>
       <c r="BB43" s="63">
         <f t="shared" si="16"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
       <c r="BC43" s="65" t="str">
         <f t="shared" si="17"/>
@@ -58688,11 +58632,11 @@
       </c>
       <c r="BH43" s="20">
         <f t="shared" si="21"/>
-        <v>68</v>
+        <v>90.25</v>
       </c>
       <c r="BI43" s="20">
         <f t="shared" si="22"/>
-        <v>84.3125</v>
+        <v>89.875</v>
       </c>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.2">
@@ -59185,6 +59129,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="AZ1:AZ2"/>
     <mergeCell ref="BA1:BA2"/>
     <mergeCell ref="BB1:BB2"/>
@@ -59195,75 +59155,69 @@
     <mergeCell ref="AW1:AW2"/>
     <mergeCell ref="AX1:AX2"/>
     <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
   </mergeCells>
   <conditionalFormatting sqref="E3:AJ3">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:L33">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:L44">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:AB33">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O38:AB44">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U33:AG33 AK3:AP47 E4:F33 M4:N33 AC4:AD33 E34:AJ37 E38:F44 M38:N44 AC38:AD44 AH38:AJ44 E45:AJ47">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="lessThan">
+  <conditionalFormatting sqref="U33:AG33 AK3:AP47 E4:F33 M4:N33 AC4:AD33 E38:F44 M38:N44 AC38:AD44 AH44:AJ44 E45:AJ47 AH38:AH43 AJ34:AJ43 E34:AI37">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE38:AG44">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE4:AJ33">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="AE4:AH33 AJ4:AJ33">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AR47">
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR3:AY47">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ47">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="lessThan">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI4:AI33">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI38:AI43">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
